--- a/logs/方案&效果记录.xlsx
+++ b/logs/方案&效果记录.xlsx
@@ -1064,7 +1064,9 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="4">
+        <v>70.36</v>
+      </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
